--- a/api/public/templates/OpenEMIS_Core_Import_Student_Absences_Period_Details_Template.xlsx
+++ b/api/public/templates/OpenEMIS_Core_Import_Student_Absences_Period_Details_Template.xlsx
@@ -99,130 +99,130 @@
     <t>Period 1</t>
   </si>
   <si>
-    <t>Creative Arts</t>
+    <t>Science</t>
   </si>
   <si>
     <t>Avory Primary School</t>
   </si>
   <si>
+    <t>Primary 2</t>
+  </si>
+  <si>
+    <t>Todd Renner</t>
+  </si>
+  <si>
+    <t>Absence - Excused</t>
+  </si>
+  <si>
+    <t>EXCUSED</t>
+  </si>
+  <si>
+    <t>Illness</t>
+  </si>
+  <si>
+    <t>SUBJECT</t>
+  </si>
+  <si>
+    <t>Spanish</t>
+  </si>
+  <si>
+    <t>Terrence Hedrick</t>
+  </si>
+  <si>
+    <t>Absence - Unexcused</t>
+  </si>
+  <si>
+    <t>UNEXCUSED</t>
+  </si>
+  <si>
+    <t>Family emergency</t>
+  </si>
+  <si>
+    <t>Physical Education</t>
+  </si>
+  <si>
+    <t>Stanley Harris</t>
+  </si>
+  <si>
+    <t>Late</t>
+  </si>
+  <si>
+    <t>LATE</t>
+  </si>
+  <si>
+    <t>Emergency</t>
+  </si>
+  <si>
+    <t>Mathematics</t>
+  </si>
+  <si>
+    <t>Timothy Wentworth</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>Expressive Arts</t>
+  </si>
+  <si>
+    <t>Thomas Schultz</t>
+  </si>
+  <si>
+    <t>Family Matter</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Tim Murphy</t>
+  </si>
+  <si>
+    <t>Personal Reasons</t>
+  </si>
+  <si>
+    <t>Artistic Design</t>
+  </si>
+  <si>
+    <t>Jason Smtih</t>
+  </si>
+  <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Thomas Cormier</t>
+  </si>
+  <si>
+    <t>Death</t>
+  </si>
+  <si>
+    <t>Aaron Butler</t>
+  </si>
+  <si>
+    <t>Medical Appointment</t>
+  </si>
+  <si>
+    <t>Aaron Clark</t>
+  </si>
+  <si>
+    <t>Thorpe Stockwell</t>
+  </si>
+  <si>
+    <t>Jannel Farmer</t>
+  </si>
+  <si>
+    <t>Janean Harpin</t>
+  </si>
+  <si>
+    <t>Janetta Welbrock</t>
+  </si>
+  <si>
+    <t>Janenna Dilloway</t>
+  </si>
+  <si>
+    <t>Jamil Blancowe</t>
+  </si>
+  <si>
     <t>Primary 1</t>
-  </si>
-  <si>
-    <t>Quintilla Layson</t>
-  </si>
-  <si>
-    <t>Absence - Excused</t>
-  </si>
-  <si>
-    <t>EXCUSED</t>
-  </si>
-  <si>
-    <t>Illness</t>
-  </si>
-  <si>
-    <t>SUBJECT</t>
-  </si>
-  <si>
-    <t>Expressive Arts</t>
-  </si>
-  <si>
-    <t>Lazaro Sawer</t>
-  </si>
-  <si>
-    <t>Absence - Unexcused</t>
-  </si>
-  <si>
-    <t>UNEXCUSED</t>
-  </si>
-  <si>
-    <t>Family emergency</t>
-  </si>
-  <si>
-    <t>Science</t>
-  </si>
-  <si>
-    <t>Hillier Baake</t>
-  </si>
-  <si>
-    <t>Late</t>
-  </si>
-  <si>
-    <t>LATE</t>
-  </si>
-  <si>
-    <t>Emergency</t>
-  </si>
-  <si>
-    <t>Social Studies</t>
-  </si>
-  <si>
-    <t>Lilith Klemps</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>Artistic Design</t>
-  </si>
-  <si>
-    <t>Reade Beed</t>
-  </si>
-  <si>
-    <t>Family Matter</t>
-  </si>
-  <si>
-    <t>Mathematics</t>
-  </si>
-  <si>
-    <t>Willi Muslim</t>
-  </si>
-  <si>
-    <t>Personal Reasons</t>
-  </si>
-  <si>
-    <t>Physical Education</t>
-  </si>
-  <si>
-    <t>Donnie Brosel</t>
-  </si>
-  <si>
-    <t>Transportation</t>
-  </si>
-  <si>
-    <t>Spanish</t>
-  </si>
-  <si>
-    <t>Vernen Lindstedt</t>
-  </si>
-  <si>
-    <t>Death</t>
-  </si>
-  <si>
-    <t>Leonanie Matoshin</t>
-  </si>
-  <si>
-    <t>Medical Appointment</t>
-  </si>
-  <si>
-    <t>Henry Beekman</t>
-  </si>
-  <si>
-    <t>Torey Shadwick</t>
-  </si>
-  <si>
-    <t>Candie Reagan</t>
-  </si>
-  <si>
-    <t>Leo Patrono</t>
-  </si>
-  <si>
-    <t>Ludovika McAllaster</t>
-  </si>
-  <si>
-    <t>Lida Danneil</t>
-  </si>
-  <si>
-    <t>Mel Mancktelow</t>
   </si>
   <si>
     <t>Kevina Etuck</t>
@@ -6206,7 +6206,7 @@
         <v>27</v>
       </c>
       <c r="F4">
-        <v>4718</v>
+        <v>4783</v>
       </c>
       <c r="G4" t="s">
         <v>28</v>
@@ -6221,7 +6221,7 @@
         <v>30</v>
       </c>
       <c r="K4">
-        <v>2382817279</v>
+        <v>1522271989</v>
       </c>
       <c r="L4" t="s">
         <v>31</v>
@@ -6249,7 +6249,7 @@
         <v>35</v>
       </c>
       <c r="F5">
-        <v>4716</v>
+        <v>4781</v>
       </c>
       <c r="G5" t="s">
         <v>28</v>
@@ -6264,7 +6264,7 @@
         <v>36</v>
       </c>
       <c r="K5">
-        <v>2382817280</v>
+        <v>1522271990</v>
       </c>
       <c r="L5" t="s">
         <v>37</v>
@@ -6288,7 +6288,7 @@
         <v>40</v>
       </c>
       <c r="F6">
-        <v>4722</v>
+        <v>4779</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -6303,7 +6303,7 @@
         <v>41</v>
       </c>
       <c r="K6">
-        <v>2382817281</v>
+        <v>1522272007</v>
       </c>
       <c r="L6" t="s">
         <v>42</v>
@@ -6327,7 +6327,7 @@
         <v>45</v>
       </c>
       <c r="F7">
-        <v>4715</v>
+        <v>4780</v>
       </c>
       <c r="G7" t="s">
         <v>28</v>
@@ -6342,7 +6342,7 @@
         <v>46</v>
       </c>
       <c r="K7">
-        <v>2382817282</v>
+        <v>1522272165</v>
       </c>
       <c r="L7"/>
       <c r="M7"/>
@@ -6362,7 +6362,7 @@
         <v>48</v>
       </c>
       <c r="F8">
-        <v>4721</v>
+        <v>4778</v>
       </c>
       <c r="G8" t="s">
         <v>28</v>
@@ -6377,7 +6377,7 @@
         <v>49</v>
       </c>
       <c r="K8">
-        <v>2382817283</v>
+        <v>1522272204</v>
       </c>
       <c r="L8"/>
       <c r="M8"/>
@@ -6397,7 +6397,7 @@
         <v>51</v>
       </c>
       <c r="F9">
-        <v>4719</v>
+        <v>4777</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
@@ -6412,7 +6412,7 @@
         <v>52</v>
       </c>
       <c r="K9">
-        <v>2382817284</v>
+        <v>1522272223</v>
       </c>
       <c r="L9"/>
       <c r="M9"/>
@@ -6432,7 +6432,7 @@
         <v>54</v>
       </c>
       <c r="F10">
-        <v>4717</v>
+        <v>4782</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -6447,7 +6447,7 @@
         <v>55</v>
       </c>
       <c r="K10">
-        <v>2382817285</v>
+        <v>1522272292</v>
       </c>
       <c r="L10"/>
       <c r="M10"/>
@@ -6463,12 +6463,8 @@
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
-      <c r="E11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11">
-        <v>4720</v>
-      </c>
+      <c r="E11"/>
+      <c r="F11"/>
       <c r="G11" t="s">
         <v>28</v>
       </c>
@@ -6479,15 +6475,15 @@
         <v>29</v>
       </c>
       <c r="J11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K11">
-        <v>2382817286</v>
+        <v>1522272350</v>
       </c>
       <c r="L11"/>
       <c r="M11"/>
       <c r="N11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O11">
         <v>9</v>
@@ -6510,15 +6506,15 @@
         <v>29</v>
       </c>
       <c r="J12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K12">
-        <v>2382817287</v>
+        <v>1522413076</v>
       </c>
       <c r="L12"/>
       <c r="M12"/>
       <c r="N12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O12">
         <v>10</v>
@@ -6541,10 +6537,10 @@
         <v>29</v>
       </c>
       <c r="J13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K13">
-        <v>2382817288</v>
+        <v>1522415305</v>
       </c>
       <c r="L13"/>
       <c r="M13"/>
@@ -6568,10 +6564,10 @@
         <v>29</v>
       </c>
       <c r="J14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K14">
-        <v>2382817289</v>
+        <v>1548403566</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
@@ -6595,10 +6591,10 @@
         <v>29</v>
       </c>
       <c r="J15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K15">
-        <v>2382817290</v>
+        <v>1548403770</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
@@ -6622,10 +6618,10 @@
         <v>29</v>
       </c>
       <c r="J16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K16">
-        <v>2382817291</v>
+        <v>1548403791</v>
       </c>
       <c r="L16"/>
       <c r="M16"/>
@@ -6649,10 +6645,10 @@
         <v>29</v>
       </c>
       <c r="J17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K17">
-        <v>2382817292</v>
+        <v>1548405194</v>
       </c>
       <c r="L17"/>
       <c r="M17"/>
@@ -6676,10 +6672,10 @@
         <v>29</v>
       </c>
       <c r="J18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K18">
-        <v>2382817293</v>
+        <v>1548405652</v>
       </c>
       <c r="L18"/>
       <c r="M18"/>
@@ -6703,10 +6699,10 @@
         <v>29</v>
       </c>
       <c r="J19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K19">
-        <v>2382817294</v>
+        <v>1548405785</v>
       </c>
       <c r="L19"/>
       <c r="M19"/>
@@ -6727,7 +6723,7 @@
         <v>2024</v>
       </c>
       <c r="I20" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J20" t="s">
         <v>69</v>
@@ -6754,7 +6750,7 @@
         <v>2024</v>
       </c>
       <c r="I21" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J21" t="s">
         <v>70</v>
@@ -6781,7 +6777,7 @@
         <v>2024</v>
       </c>
       <c r="I22" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J22" t="s">
         <v>71</v>
@@ -6808,7 +6804,7 @@
         <v>2024</v>
       </c>
       <c r="I23" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J23" t="s">
         <v>72</v>
@@ -6835,7 +6831,7 @@
         <v>2024</v>
       </c>
       <c r="I24" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J24" t="s">
         <v>73</v>
@@ -6862,7 +6858,7 @@
         <v>2024</v>
       </c>
       <c r="I25" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J25" t="s">
         <v>74</v>
@@ -6889,7 +6885,7 @@
         <v>2024</v>
       </c>
       <c r="I26" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J26" t="s">
         <v>75</v>
@@ -6916,7 +6912,7 @@
         <v>2024</v>
       </c>
       <c r="I27" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J27" t="s">
         <v>76</v>
@@ -6943,7 +6939,7 @@
         <v>2024</v>
       </c>
       <c r="I28" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J28" t="s">
         <v>77</v>
@@ -6970,7 +6966,7 @@
         <v>2024</v>
       </c>
       <c r="I29" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J29" t="s">
         <v>78</v>
@@ -6997,7 +6993,7 @@
         <v>2024</v>
       </c>
       <c r="I30" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J30" t="s">
         <v>79</v>
@@ -7024,7 +7020,7 @@
         <v>2024</v>
       </c>
       <c r="I31" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J31" t="s">
         <v>80</v>
@@ -7051,7 +7047,7 @@
         <v>2024</v>
       </c>
       <c r="I32" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J32" t="s">
         <v>81</v>
@@ -7078,7 +7074,7 @@
         <v>2024</v>
       </c>
       <c r="I33" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="J33" t="s">
         <v>82</v>
